--- a/human_resources_forms/012_worker_feedback_summary_request_form--human_resources_forms.xlsx
+++ b/human_resources_forms/012_worker_feedback_summary_request_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'for_employee_feedback'}</t>
+          <t>for_employee_feedback</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'For employee feedback'}</t>
+          <t>For employee feedback</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'for_performance_evaluation'}</t>
+          <t>for_performance_evaluation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'For performance evaluation'}</t>
+          <t>For performance evaluation</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'to_improve_employee_experience'}</t>
+          <t>to_improve_employee_experience</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'To improve employee experience'}</t>
+          <t>To improve employee experience</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'to_identify_areas_for_improvement'}</t>
+          <t>to_identify_areas_for_improvement</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'To identify areas for improvement'}</t>
+          <t>To identify areas for improvement</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_'to_improve_employee_experience'}</t>
+          <t>to_improve_employee_experience</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': 'To improve employee experience'}</t>
+          <t>To improve employee experience</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_'to_identify_areas_for_improvement'}</t>
+          <t>to_identify_areas_for_improvement</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': 'To identify areas for improvement'}</t>
+          <t>To identify areas for improvement</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
